--- a/InputData/elec/MCF/Maximum Capacity Factor.xlsx
+++ b/InputData/elec/MCF/Maximum Capacity Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\elec\MCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\ND\elec\MCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF5E761-3510-4551-BBBD-14D4B578101B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{821472B8-8A76-49D9-A0D4-3B6E02EFDB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="12" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>nuclear</t>
   </si>
@@ -161,15 +161,15 @@
   </si>
   <si>
     <t>in any given hour. This is used for non-variable plant types, including hydro. We apply</t>
+  </si>
+  <si>
+    <t>North Dakota</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-  </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -322,13 +322,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -336,6 +335,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Body: normal cell" xfId="5" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -769,6 +769,12 @@
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="8">
+        <v>45320</v>
+      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G2" s="2"/>
@@ -801,7 +807,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E6" s="1"/>
@@ -826,7 +832,7 @@
       <c r="A10" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="4"/>
+      <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -864,231 +870,214 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" customWidth="1"/>
     <col min="2" max="3" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="5"/>
-      <c r="C1" s="7"/>
+      <c r="C1" s="6"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2">
         <v>0.85</v>
       </c>
-      <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C3" s="3"/>
+      <c r="B3">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C4" s="3"/>
+      <c r="B4">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="3">
-        <v>0.91</v>
-      </c>
-      <c r="C5" s="3"/>
+      <c r="B5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C6" s="3"/>
+      <c r="B6">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>0</v>
       </c>
-      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>0</v>
       </c>
-      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>0</v>
       </c>
-      <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C10" s="3"/>
+      <c r="B10">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C11" s="3"/>
+      <c r="B11">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C12" s="3"/>
+      <c r="B12">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C13" s="3"/>
+      <c r="B13">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C14" s="3"/>
+      <c r="B14">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15">
         <v>0</v>
       </c>
-      <c r="C15" s="3"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C16" s="3"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19">
         <f>B2</f>
         <v>0.85</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20">
         <f>B4</f>
         <v>0.95</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21">
         <f>B10</f>
         <v>0.95</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22">
         <f>B14</f>
         <v>0.95</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23">
         <f>B5</f>
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24">
         <f>B4</f>
         <v>0.95</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25">
         <f>B4</f>
         <v>0.95</v>
       </c>

--- a/InputData/elec/MCF/Maximum Capacity Factor.xlsx
+++ b/InputData/elec/MCF/Maximum Capacity Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\ND\elec\MCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\ND\elec\MCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{875C097C-91E9-4AD9-9510-E3D8C6E6879A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{62147734-BEB3-4939-9E4F-008B7791F767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12510" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="12" r:id="rId1"/>
@@ -1461,6 +1461,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Header Descriptions"/>
       <sheetName val="2019 NQC List"/>
@@ -1482,6 +1485,9 @@
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Information"/>
       <sheetName val="Request Type 1-2"/>
@@ -1852,15 +1858,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" customWidth="1"/>
-    <col min="2" max="2" width="50.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="49.54296875" customWidth="1"/>
-    <col min="8" max="8" width="53.7265625" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.5703125" customWidth="1"/>
+    <col min="8" max="8" width="53.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -1868,13 +1874,13 @@
         <v>135</v>
       </c>
       <c r="C1" s="98">
-        <v>45420</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.75">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -1884,7 +1890,7 @@
       <c r="E3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
         <v>22</v>
@@ -1892,7 +1898,7 @@
       <c r="E4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="2">
         <v>2019</v>
@@ -1900,7 +1906,7 @@
       <c r="E5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
         <v>23</v>
@@ -1908,99 +1914,99 @@
       <c r="E6" s="1"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" s="97" t="s">
         <v>129</v>
       </c>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>130</v>
       </c>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>131</v>
       </c>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
         <v>2024</v>
       </c>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>132</v>
       </c>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>133</v>
       </c>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>128</v>
       </c>
@@ -2022,14 +2028,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0150863A-DAB8-46CE-A81F-C1B3C520912B}">
   <dimension ref="A1:N158"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="65.26953125" style="54" customWidth="1"/>
+    <col min="1" max="1" width="65.28515625" style="54" customWidth="1"/>
     <col min="2" max="2" width="2" style="54" customWidth="1"/>
-    <col min="3" max="8" width="8.453125" style="5" customWidth="1"/>
+    <col min="3" max="8" width="8.42578125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -2038,7 +2044,7 @@
       <c r="F1" s="4"/>
       <c r="G1"/>
     </row>
-    <row r="2" spans="1:14" ht="25.25" x14ac:dyDescent="1.05">
+    <row r="2" spans="1:14" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="102" t="s">
         <v>35</v>
       </c>
@@ -2049,7 +2055,7 @@
       <c r="F2" s="102"/>
       <c r="G2" s="102"/>
     </row>
-    <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.8">
+    <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2062,7 +2068,7 @@
       <c r="M3" s="103"/>
       <c r="N3" s="103"/>
     </row>
-    <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.8">
+    <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="104" t="s">
         <v>36</v>
       </c>
@@ -2073,7 +2079,7 @@
       <c r="F4" s="104"/>
       <c r="G4" s="104"/>
     </row>
-    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.8">
+    <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="103"/>
       <c r="C5" s="103"/>
@@ -2082,7 +2088,7 @@
       <c r="F5" s="4"/>
       <c r="G5"/>
     </row>
-    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
@@ -2093,7 +2099,7 @@
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="105"/>
       <c r="B7" s="105"/>
       <c r="C7" s="105"/>
@@ -2102,7 +2108,7 @@
       <c r="F7" s="105"/>
       <c r="G7" s="105"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -2111,7 +2117,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:14" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>38</v>
       </c>
@@ -2120,7 +2126,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="10" spans="1:14" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>40</v>
       </c>
@@ -2148,7 +2154,7 @@
       </c>
       <c r="J10" s="15"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>41</v>
       </c>
@@ -2176,7 +2182,7 @@
       </c>
       <c r="J11" s="22"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
         <v>42</v>
       </c>
@@ -2204,7 +2210,7 @@
       </c>
       <c r="J12" s="27"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>43</v>
       </c>
@@ -2232,7 +2238,7 @@
       </c>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
         <v>44</v>
       </c>
@@ -2260,7 +2266,7 @@
       </c>
       <c r="J14" s="33"/>
     </row>
-    <row r="15" spans="1:14" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34" t="s">
         <v>45</v>
       </c>
@@ -2288,7 +2294,7 @@
       </c>
       <c r="J15" s="33"/>
     </row>
-    <row r="16" spans="1:14" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
       <c r="C16" s="39"/>
@@ -2298,7 +2304,7 @@
       <c r="G16" s="39"/>
       <c r="H16" s="40"/>
     </row>
-    <row r="17" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="17" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>46</v>
       </c>
@@ -2326,7 +2332,7 @@
       </c>
       <c r="J17" s="15"/>
     </row>
-    <row r="18" spans="1:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="41" t="s">
         <v>47</v>
       </c>
@@ -2354,7 +2360,7 @@
       </c>
       <c r="J18" s="45"/>
     </row>
-    <row r="19" spans="1:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17"/>
       <c r="B19" s="17"/>
       <c r="C19" s="46"/>
@@ -2364,7 +2370,7 @@
       <c r="G19" s="46"/>
       <c r="H19" s="47"/>
     </row>
-    <row r="20" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="20" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>48</v>
       </c>
@@ -2392,7 +2398,7 @@
       </c>
       <c r="J20" s="15"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>49</v>
       </c>
@@ -2420,7 +2426,7 @@
       </c>
       <c r="J21" s="50"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="23" t="s">
         <v>50</v>
       </c>
@@ -2434,7 +2440,7 @@
       <c r="I22" s="52"/>
       <c r="J22" s="50"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="53" t="s">
         <v>51</v>
       </c>
@@ -2461,7 +2467,7 @@
       </c>
       <c r="J23" s="50"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="55" t="s">
         <v>52</v>
       </c>
@@ -2489,7 +2495,7 @@
       </c>
       <c r="J24" s="50"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>53</v>
       </c>
@@ -2503,7 +2509,7 @@
       <c r="I25" s="49"/>
       <c r="J25" s="50"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="55" t="s">
         <v>54</v>
       </c>
@@ -2531,7 +2537,7 @@
       </c>
       <c r="J26" s="50"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="53" t="s">
         <v>55</v>
       </c>
@@ -2550,7 +2556,7 @@
       <c r="I27" s="49"/>
       <c r="J27" s="50"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="55" t="s">
         <v>56</v>
       </c>
@@ -2578,7 +2584,7 @@
       </c>
       <c r="J28" s="50"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="53" t="s">
         <v>57</v>
       </c>
@@ -2599,7 +2605,7 @@
       <c r="I29" s="49"/>
       <c r="J29" s="50"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="55" t="s">
         <v>58</v>
       </c>
@@ -2627,7 +2633,7 @@
       </c>
       <c r="J30" s="50"/>
     </row>
-    <row r="31" spans="1:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="31" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="57" t="s">
         <v>59</v>
       </c>
@@ -2655,7 +2661,7 @@
       </c>
       <c r="J31" s="50"/>
     </row>
-    <row r="32" spans="1:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="32" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="17"/>
       <c r="B32" s="17"/>
       <c r="C32" s="61"/>
@@ -2665,7 +2671,7 @@
       <c r="G32" s="61"/>
       <c r="H32" s="61"/>
     </row>
-    <row r="33" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="33" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>60</v>
       </c>
@@ -2693,7 +2699,7 @@
       </c>
       <c r="J33" s="15"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
         <v>61</v>
       </c>
@@ -2721,7 +2727,7 @@
       </c>
       <c r="J34" s="64"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="23" t="s">
         <v>62</v>
       </c>
@@ -2749,7 +2755,7 @@
       </c>
       <c r="J35" s="64"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="53" t="s">
         <v>63</v>
       </c>
@@ -2777,7 +2783,7 @@
       </c>
       <c r="J36" s="64"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="55" t="s">
         <v>64</v>
       </c>
@@ -2805,7 +2811,7 @@
       </c>
       <c r="J37" s="64"/>
     </row>
-    <row r="38" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="38" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A38" s="53" t="s">
         <v>65</v>
       </c>
@@ -2833,7 +2839,7 @@
       </c>
       <c r="J38" s="64"/>
     </row>
-    <row r="39" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="39" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A39" s="55" t="s">
         <v>66</v>
       </c>
@@ -2861,7 +2867,7 @@
       </c>
       <c r="J39" s="64"/>
     </row>
-    <row r="40" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="40" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A40" s="53" t="s">
         <v>67</v>
       </c>
@@ -2889,7 +2895,7 @@
       </c>
       <c r="J40" s="64"/>
     </row>
-    <row r="41" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="41" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A41" s="55" t="s">
         <v>68</v>
       </c>
@@ -2917,7 +2923,7 @@
       </c>
       <c r="J41" s="64"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
         <v>69</v>
       </c>
@@ -2944,7 +2950,7 @@
       </c>
       <c r="J42" s="64"/>
     </row>
-    <row r="43" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="43" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A43" s="55" t="s">
         <v>70</v>
       </c>
@@ -2972,7 +2978,7 @@
       </c>
       <c r="J43" s="64"/>
     </row>
-    <row r="44" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="44" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A44" s="53" t="s">
         <v>71</v>
       </c>
@@ -3000,7 +3006,7 @@
       </c>
       <c r="J44" s="64"/>
     </row>
-    <row r="45" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="45" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A45" s="55" t="s">
         <v>72</v>
       </c>
@@ -3028,7 +3034,7 @@
       </c>
       <c r="J45" s="64"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
         <v>73</v>
       </c>
@@ -3055,7 +3061,7 @@
       </c>
       <c r="J46" s="64"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="23" t="s">
         <v>74</v>
       </c>
@@ -3083,7 +3089,7 @@
       </c>
       <c r="J47" s="64"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
         <v>75</v>
       </c>
@@ -3110,7 +3116,7 @@
       </c>
       <c r="J48" s="64"/>
     </row>
-    <row r="49" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="49" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A49" s="55" t="s">
         <v>76</v>
       </c>
@@ -3138,7 +3144,7 @@
       </c>
       <c r="J49" s="64"/>
     </row>
-    <row r="50" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="50" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A50" s="53" t="s">
         <v>77</v>
       </c>
@@ -3166,7 +3172,7 @@
       </c>
       <c r="J50" s="64"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="55" t="s">
         <v>78</v>
       </c>
@@ -3194,7 +3200,7 @@
       </c>
       <c r="J51" s="64"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
         <v>79</v>
       </c>
@@ -3221,7 +3227,7 @@
       </c>
       <c r="J52" s="64"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="23" t="s">
         <v>80</v>
       </c>
@@ -3249,7 +3255,7 @@
       </c>
       <c r="J53" s="64"/>
     </row>
-    <row r="54" spans="1:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="54" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="72" t="s">
         <v>81</v>
       </c>
@@ -3277,7 +3283,7 @@
       </c>
       <c r="J54" s="64"/>
     </row>
-    <row r="55" spans="1:10" ht="16.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="55" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="17"/>
       <c r="B55" s="17"/>
       <c r="C55" s="62"/>
@@ -3287,7 +3293,7 @@
       <c r="G55" s="62"/>
       <c r="H55" s="62"/>
     </row>
-    <row r="56" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="56" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>82</v>
       </c>
@@ -3315,7 +3321,7 @@
       </c>
       <c r="J56" s="15"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
         <v>61</v>
       </c>
@@ -3343,7 +3349,7 @@
       </c>
       <c r="J57" s="33"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="23" t="s">
         <v>62</v>
       </c>
@@ -3371,7 +3377,7 @@
       </c>
       <c r="J58" s="77"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="53" t="s">
         <v>63</v>
       </c>
@@ -3399,7 +3405,7 @@
       </c>
       <c r="J59" s="77"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="55" t="s">
         <v>64</v>
       </c>
@@ -3427,7 +3433,7 @@
       </c>
       <c r="J60" s="77"/>
     </row>
-    <row r="61" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="61" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A61" s="53" t="s">
         <v>65</v>
       </c>
@@ -3455,7 +3461,7 @@
       </c>
       <c r="J61" s="77"/>
     </row>
-    <row r="62" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="62" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A62" s="55" t="s">
         <v>66</v>
       </c>
@@ -3483,7 +3489,7 @@
       </c>
       <c r="J62" s="77"/>
     </row>
-    <row r="63" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="63" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A63" s="53" t="s">
         <v>67</v>
       </c>
@@ -3511,7 +3517,7 @@
       </c>
       <c r="J63" s="77"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="23" t="s">
         <v>69</v>
       </c>
@@ -3539,7 +3545,7 @@
       </c>
       <c r="J64" s="77"/>
     </row>
-    <row r="65" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="65" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A65" s="53" t="s">
         <v>70</v>
       </c>
@@ -3567,7 +3573,7 @@
       </c>
       <c r="J65" s="77"/>
     </row>
-    <row r="66" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="66" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A66" s="78" t="s">
         <v>71</v>
       </c>
@@ -3595,7 +3601,7 @@
       </c>
       <c r="J66" s="77"/>
     </row>
-    <row r="67" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="67" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A67" s="53" t="s">
         <v>72</v>
       </c>
@@ -3623,7 +3629,7 @@
       </c>
       <c r="J67" s="77"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="23" t="s">
         <v>73</v>
       </c>
@@ -3651,7 +3657,7 @@
       </c>
       <c r="J68" s="77"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="16" t="s">
         <v>74</v>
       </c>
@@ -3679,7 +3685,7 @@
       </c>
       <c r="J69" s="77"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="23" t="s">
         <v>75</v>
       </c>
@@ -3707,7 +3713,7 @@
       </c>
       <c r="J70" s="77"/>
     </row>
-    <row r="71" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="71" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A71" s="53" t="s">
         <v>76</v>
       </c>
@@ -3735,7 +3741,7 @@
       </c>
       <c r="J71" s="77"/>
     </row>
-    <row r="72" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="72" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A72" s="79" t="s">
         <v>77</v>
       </c>
@@ -3763,7 +3769,7 @@
       </c>
       <c r="J72" s="77"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="53" t="s">
         <v>78</v>
       </c>
@@ -3791,7 +3797,7 @@
       </c>
       <c r="J73" s="77"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="23" t="s">
         <v>80</v>
       </c>
@@ -3819,7 +3825,7 @@
       </c>
       <c r="J74" s="77"/>
     </row>
-    <row r="75" spans="1:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="75" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="80" t="s">
         <v>81</v>
       </c>
@@ -3847,7 +3853,7 @@
       </c>
       <c r="J75" s="77"/>
     </row>
-    <row r="76" spans="1:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="76" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="34"/>
       <c r="B76" s="35"/>
       <c r="C76" s="84"/>
@@ -3859,7 +3865,7 @@
       <c r="I76" s="84"/>
       <c r="J76" s="77"/>
     </row>
-    <row r="77" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="77" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="11" t="s">
         <v>83</v>
       </c>
@@ -3887,7 +3893,7 @@
       </c>
       <c r="J77" s="15"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="16" t="s">
         <v>61</v>
       </c>
@@ -3915,7 +3921,7 @@
       </c>
       <c r="J78" s="33"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="23" t="s">
         <v>62</v>
       </c>
@@ -3943,7 +3949,7 @@
       </c>
       <c r="J79" s="77"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="53" t="s">
         <v>63</v>
       </c>
@@ -3971,7 +3977,7 @@
       </c>
       <c r="J80" s="77"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="55" t="s">
         <v>64</v>
       </c>
@@ -3999,7 +4005,7 @@
       </c>
       <c r="J81" s="77"/>
     </row>
-    <row r="82" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="82" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A82" s="53" t="s">
         <v>65</v>
       </c>
@@ -4027,7 +4033,7 @@
       </c>
       <c r="J82" s="77"/>
     </row>
-    <row r="83" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="83" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A83" s="55" t="s">
         <v>66</v>
       </c>
@@ -4055,7 +4061,7 @@
       </c>
       <c r="J83" s="77"/>
     </row>
-    <row r="84" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="84" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A84" s="53" t="s">
         <v>67</v>
       </c>
@@ -4083,7 +4089,7 @@
       </c>
       <c r="J84" s="77"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="23" t="s">
         <v>69</v>
       </c>
@@ -4111,7 +4117,7 @@
       </c>
       <c r="J85" s="77"/>
     </row>
-    <row r="86" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="86" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A86" s="53" t="s">
         <v>70</v>
       </c>
@@ -4139,7 +4145,7 @@
       </c>
       <c r="J86" s="77"/>
     </row>
-    <row r="87" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="87" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A87" s="78" t="s">
         <v>71</v>
       </c>
@@ -4167,7 +4173,7 @@
       </c>
       <c r="J87" s="77"/>
     </row>
-    <row r="88" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="88" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A88" s="53" t="s">
         <v>72</v>
       </c>
@@ -4195,7 +4201,7 @@
       </c>
       <c r="J88" s="77"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="23" t="s">
         <v>73</v>
       </c>
@@ -4223,7 +4229,7 @@
       </c>
       <c r="J89" s="77"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="16" t="s">
         <v>74</v>
       </c>
@@ -4251,7 +4257,7 @@
       </c>
       <c r="J90" s="77"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="23" t="s">
         <v>75</v>
       </c>
@@ -4279,7 +4285,7 @@
       </c>
       <c r="J91" s="77"/>
     </row>
-    <row r="92" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="92" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A92" s="53" t="s">
         <v>76</v>
       </c>
@@ -4307,7 +4313,7 @@
       </c>
       <c r="J92" s="77"/>
     </row>
-    <row r="93" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="93" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A93" s="79" t="s">
         <v>77</v>
       </c>
@@ -4335,7 +4341,7 @@
       </c>
       <c r="J93" s="77"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="53" t="s">
         <v>78</v>
       </c>
@@ -4363,7 +4369,7 @@
       </c>
       <c r="J94" s="77"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="23" t="s">
         <v>80</v>
       </c>
@@ -4391,7 +4397,7 @@
       </c>
       <c r="J95" s="77"/>
     </row>
-    <row r="96" spans="1:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="96" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="80" t="s">
         <v>81</v>
       </c>
@@ -4419,7 +4425,7 @@
       </c>
       <c r="J96" s="77"/>
     </row>
-    <row r="97" spans="1:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="97" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="17"/>
       <c r="B97" s="17"/>
       <c r="C97" s="62"/>
@@ -4429,7 +4435,7 @@
       <c r="G97" s="62"/>
       <c r="H97" s="62"/>
     </row>
-    <row r="98" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="98" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="11" t="s">
         <v>84</v>
       </c>
@@ -4457,7 +4463,7 @@
       </c>
       <c r="J98" s="15"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="53" t="s">
         <v>85</v>
       </c>
@@ -4484,7 +4490,7 @@
       </c>
       <c r="J99" s="77"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="55" t="s">
         <v>86</v>
       </c>
@@ -4512,7 +4518,7 @@
       </c>
       <c r="J100" s="77"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="53" t="s">
         <v>87</v>
       </c>
@@ -4539,7 +4545,7 @@
       </c>
       <c r="J101" s="77"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="55" t="s">
         <v>88</v>
       </c>
@@ -4567,7 +4573,7 @@
       </c>
       <c r="J102" s="77"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="53" t="s">
         <v>89</v>
       </c>
@@ -4594,7 +4600,7 @@
       </c>
       <c r="J103" s="77"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="55" t="s">
         <v>90</v>
       </c>
@@ -4622,7 +4628,7 @@
       </c>
       <c r="J104" s="77"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="53" t="s">
         <v>91</v>
       </c>
@@ -4649,7 +4655,7 @@
       </c>
       <c r="J105" s="77"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="56" t="s">
         <v>92</v>
       </c>
@@ -4677,7 +4683,7 @@
       </c>
       <c r="J106" s="77"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="54" t="s">
         <v>93</v>
       </c>
@@ -4704,7 +4710,7 @@
       </c>
       <c r="J107" s="64"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="56" t="s">
         <v>94</v>
       </c>
@@ -4731,7 +4737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="54" t="s">
         <v>95</v>
       </c>
@@ -4758,7 +4764,7 @@
       </c>
       <c r="J109" s="15"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="56" t="s">
         <v>96</v>
       </c>
@@ -4786,7 +4792,7 @@
       </c>
       <c r="J110" s="64"/>
     </row>
-    <row r="111" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="111" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A111" s="54" t="s">
         <v>97</v>
       </c>
@@ -4814,7 +4820,7 @@
       </c>
       <c r="J111" s="64"/>
     </row>
-    <row r="112" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="112" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A112" s="56" t="s">
         <v>98</v>
       </c>
@@ -4842,7 +4848,7 @@
       </c>
       <c r="J112" s="64"/>
     </row>
-    <row r="113" spans="1:10" s="69" customFormat="1" ht="15.25" thickBot="1" x14ac:dyDescent="0.85">
+    <row r="113" spans="1:10" s="69" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="80" t="s">
         <v>81</v>
       </c>
@@ -4870,7 +4876,7 @@
       </c>
       <c r="J113" s="64"/>
     </row>
-    <row r="114" spans="1:10" s="69" customFormat="1" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="114" spans="1:10" s="69" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="54"/>
       <c r="B114" s="54"/>
       <c r="C114" s="62"/>
@@ -4882,7 +4888,7 @@
       <c r="I114"/>
       <c r="J114" s="64"/>
     </row>
-    <row r="115" spans="1:10" s="69" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="115" spans="1:10" s="69" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="11" t="s">
         <v>99</v>
       </c>
@@ -4910,7 +4916,7 @@
       </c>
       <c r="J115" s="64"/>
     </row>
-    <row r="116" spans="1:10" s="69" customFormat="1" ht="14.5" x14ac:dyDescent="0.7">
+    <row r="116" spans="1:10" s="69" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="16" t="s">
         <v>61</v>
       </c>
@@ -4938,7 +4944,7 @@
       </c>
       <c r="J116" s="64"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="23" t="s">
         <v>62</v>
       </c>
@@ -4966,7 +4972,7 @@
       </c>
       <c r="J117" s="88"/>
     </row>
-    <row r="118" spans="1:10" s="69" customFormat="1" ht="14.5" x14ac:dyDescent="0.7">
+    <row r="118" spans="1:10" s="69" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="53" t="s">
         <v>63</v>
       </c>
@@ -4994,7 +5000,7 @@
       </c>
       <c r="J118" s="64"/>
     </row>
-    <row r="119" spans="1:10" s="69" customFormat="1" ht="14.5" x14ac:dyDescent="0.7">
+    <row r="119" spans="1:10" s="69" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="55" t="s">
         <v>100</v>
       </c>
@@ -5022,7 +5028,7 @@
       </c>
       <c r="J119" s="64"/>
     </row>
-    <row r="120" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="120" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A120" s="53" t="s">
         <v>64</v>
       </c>
@@ -5050,7 +5056,7 @@
       </c>
       <c r="J120" s="64"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="55" t="s">
         <v>65</v>
       </c>
@@ -5078,7 +5084,7 @@
       </c>
       <c r="J121" s="64"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="53" t="s">
         <v>66</v>
       </c>
@@ -5105,7 +5111,7 @@
       </c>
       <c r="J122" s="64"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="55" t="s">
         <v>67</v>
       </c>
@@ -5133,7 +5139,7 @@
       </c>
       <c r="J123" s="64"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="53" t="s">
         <v>68</v>
       </c>
@@ -5160,7 +5166,7 @@
       </c>
       <c r="J124" s="64"/>
     </row>
-    <row r="125" spans="1:10" s="69" customFormat="1" ht="14.5" x14ac:dyDescent="0.7">
+    <row r="125" spans="1:10" s="69" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="23" t="s">
         <v>69</v>
       </c>
@@ -5188,7 +5194,7 @@
       </c>
       <c r="J125" s="64"/>
     </row>
-    <row r="126" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.65">
+    <row r="126" spans="1:10" s="69" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A126" s="53" t="s">
         <v>101</v>
       </c>
@@ -5216,7 +5222,7 @@
       </c>
       <c r="J126" s="64"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="55" t="s">
         <v>71</v>
       </c>
@@ -5244,7 +5250,7 @@
       </c>
       <c r="J127" s="64"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="53" t="s">
         <v>72</v>
       </c>
@@ -5271,7 +5277,7 @@
       </c>
       <c r="J128" s="64"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="23" t="s">
         <v>73</v>
       </c>
@@ -5299,7 +5305,7 @@
       </c>
       <c r="J129" s="64"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="16" t="s">
         <v>74</v>
       </c>
@@ -5326,7 +5332,7 @@
       </c>
       <c r="J130" s="64"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="23" t="s">
         <v>75</v>
       </c>
@@ -5354,7 +5360,7 @@
       </c>
       <c r="J131" s="64"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="53" t="s">
         <v>76</v>
       </c>
@@ -5380,7 +5386,7 @@
         <v>1060.4055484272631</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="55" t="s">
         <v>77</v>
       </c>
@@ -5408,7 +5414,7 @@
       </c>
       <c r="J133" s="15"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="53" t="s">
         <v>78</v>
       </c>
@@ -5435,7 +5441,7 @@
       </c>
       <c r="J134" s="64"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="23" t="s">
         <v>79</v>
       </c>
@@ -5463,7 +5469,7 @@
       </c>
       <c r="J135" s="64"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="16" t="s">
         <v>80</v>
       </c>
@@ -5490,7 +5496,7 @@
       </c>
       <c r="J136" s="64"/>
     </row>
-    <row r="137" spans="1:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="137" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="89" t="s">
         <v>81</v>
       </c>
@@ -5518,7 +5524,7 @@
       </c>
       <c r="J137" s="64"/>
     </row>
-    <row r="138" spans="1:10" ht="16.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="138" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="17"/>
       <c r="B138" s="17"/>
       <c r="C138" s="62"/>
@@ -5529,7 +5535,7 @@
       <c r="H138" s="62"/>
       <c r="J138" s="64"/>
     </row>
-    <row r="139" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="139" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="11" t="s">
         <v>102</v>
       </c>
@@ -5557,7 +5563,7 @@
       </c>
       <c r="J139" s="64"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="16" t="s">
         <v>103</v>
       </c>
@@ -5585,7 +5591,7 @@
       </c>
       <c r="J140" s="64"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="55" t="s">
         <v>104</v>
       </c>
@@ -5599,7 +5605,7 @@
       <c r="I141" s="66"/>
       <c r="J141" s="64"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="53" t="s">
         <v>105</v>
       </c>
@@ -5620,7 +5626,7 @@
       <c r="I142" s="63"/>
       <c r="J142" s="64"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="55" t="s">
         <v>106</v>
       </c>
@@ -5640,7 +5646,7 @@
       <c r="I143" s="66"/>
       <c r="J143" s="64"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="53" t="s">
         <v>107</v>
       </c>
@@ -5667,7 +5673,7 @@
       </c>
       <c r="J144" s="64"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="55" t="s">
         <v>108</v>
       </c>
@@ -5689,7 +5695,7 @@
       <c r="I145" s="66"/>
       <c r="J145" s="64"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="53" t="s">
         <v>109</v>
       </c>
@@ -5716,7 +5722,7 @@
       </c>
       <c r="J146" s="64"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="55" t="s">
         <v>110</v>
       </c>
@@ -5744,7 +5750,7 @@
       </c>
       <c r="J147" s="64"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="53" t="s">
         <v>105</v>
       </c>
@@ -5771,7 +5777,7 @@
       </c>
       <c r="J148" s="64"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="55" t="s">
         <v>107</v>
       </c>
@@ -5799,7 +5805,7 @@
       </c>
       <c r="J149" s="30"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="53" t="s">
         <v>109</v>
       </c>
@@ -5825,7 +5831,7 @@
         <v>39.010000009234588</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="23" t="s">
         <v>111</v>
       </c>
@@ -5852,7 +5858,7 @@
         <v>5.2116030849019062</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="53" t="s">
         <v>112</v>
       </c>
@@ -5872,7 +5878,7 @@
       <c r="H152" s="62"/>
       <c r="I152" s="63"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="55" t="s">
         <v>113</v>
       </c>
@@ -5899,7 +5905,7 @@
         <v>2.5205571355626204</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="53" t="s">
         <v>114</v>
       </c>
@@ -5925,7 +5931,7 @@
         <v>2.6910459493392862</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="55"/>
       <c r="B155" s="56"/>
       <c r="C155" s="65"/>
@@ -5936,7 +5942,7 @@
       <c r="H155" s="65"/>
       <c r="I155" s="66"/>
     </row>
-    <row r="156" spans="1:10" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="156" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="34" t="s">
         <v>115</v>
       </c>
@@ -5963,7 +5969,7 @@
         <v>7.8382324901165461</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C157" s="28"/>
       <c r="D157" s="28"/>
       <c r="E157" s="28"/>
@@ -5972,7 +5978,7 @@
       <c r="H157" s="28"/>
       <c r="I157" s="28"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="54" t="s">
         <v>116</v>
       </c>
@@ -5995,12 +6001,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E39369-50AE-4D5B-A91E-C3BF3A8489A4}">
   <dimension ref="A1:AE9"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18.75" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="1" spans="1:31" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="13">
         <v>2028</v>
       </c>
@@ -6023,7 +6029,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>117</v>
       </c>
@@ -6056,7 +6062,7 @@
         <v>0.42851499116440761</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>118</v>
       </c>
@@ -6089,12 +6095,12 @@
         <v>0.72106646255644558</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>117</v>
       </c>
@@ -6127,7 +6133,7 @@
         <v>0.59511818843685693</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>119</v>
       </c>
@@ -6222,7 +6228,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>117</v>
       </c>
@@ -6355,14 +6361,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0277EEC5-A757-48AB-8FE9-C61BFB5A988F}">
   <dimension ref="A1:AE27"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>121</v>
       </c>
@@ -6457,7 +6463,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -6552,7 +6558,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -6647,7 +6653,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>122</v>
       </c>
@@ -6742,7 +6748,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -6837,7 +6843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -6932,7 +6938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -7027,7 +7033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -7122,7 +7128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -7217,7 +7223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -7312,7 +7318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>123</v>
       </c>
@@ -7407,7 +7413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -7502,7 +7508,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -7597,7 +7603,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -7692,7 +7698,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -7787,7 +7793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -7882,7 +7888,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -7977,7 +7983,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -8072,7 +8078,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -8167,7 +8173,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -8262,7 +8268,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -8357,7 +8363,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -8452,7 +8458,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -8547,7 +8553,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -8642,7 +8648,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -8748,13 +8754,13 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.453125" customWidth="1"/>
+    <col min="1" max="1" width="26.42578125" customWidth="1"/>
     <col min="2" max="3" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="99" t="s">
         <v>16</v>
       </c>
@@ -8849,7 +8855,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -8944,7 +8950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -9039,7 +9045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -9134,7 +9140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -9229,7 +9235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -9324,7 +9330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -9419,7 +9425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -9514,7 +9520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -9609,7 +9615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -9704,7 +9710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -9799,7 +9805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -9894,7 +9900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -9989,7 +9995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -10084,7 +10090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -10179,7 +10185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -10274,7 +10280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -10369,7 +10375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -10464,7 +10470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -10559,7 +10565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -10654,7 +10660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -10749,7 +10755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -10844,7 +10850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -10939,7 +10945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="101" t="s">
         <v>32</v>
       </c>
@@ -11034,7 +11040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="101" t="s">
         <v>33</v>
       </c>
